--- a/12623846.xlxs.xlsx
+++ b/12623846.xlxs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sachi\Desktop\CAP776\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE6C2A2B-34FB-423D-A470-EA7277EA8648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246332AF-1B0C-408E-AC20-BCDD6E89C5E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -373,6 +373,15 @@
   </si>
   <si>
     <t>spent the day attending online classes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">excited for my brother's engagement </t>
+  </si>
+  <si>
+    <t xml:space="preserve">went to ambala with my family for shopping </t>
+  </si>
+  <si>
+    <t xml:space="preserve">studied for my upcoming midterms </t>
   </si>
 </sst>
 </file>
@@ -3495,71 +3504,143 @@
         <v>110</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+    <row r="57" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A57" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B57" s="14">
+        <v>450</v>
+      </c>
+      <c r="C57" s="14">
+        <v>30</v>
+      </c>
+      <c r="D57" s="14">
+        <v>30</v>
+      </c>
+      <c r="E57" s="14">
+        <v>30</v>
+      </c>
+      <c r="F57" s="14">
+        <v>0</v>
+      </c>
+      <c r="G57" s="14">
+        <v>0</v>
+      </c>
+      <c r="H57" s="14">
+        <v>400</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+        <v>500</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A58" s="13">
+        <v>46303</v>
+      </c>
+      <c r="B58" s="14">
+        <v>500</v>
+      </c>
+      <c r="C58" s="14">
+        <v>60</v>
+      </c>
+      <c r="D58" s="14">
+        <v>120</v>
+      </c>
+      <c r="E58" s="14">
+        <v>30</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
+        <v>500</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+        <v>230</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A59" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B59" s="14">
+        <v>500</v>
+      </c>
+      <c r="C59" s="14">
+        <v>60</v>
+      </c>
+      <c r="D59" s="14">
+        <v>120</v>
+      </c>
+      <c r="E59" s="14">
+        <v>20</v>
+      </c>
+      <c r="F59" s="14">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14">
+        <v>0</v>
+      </c>
+      <c r="H59" s="14">
+        <v>500</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
+        <v>240</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" s="13"/>

--- a/12623846.xlxs.xlsx
+++ b/12623846.xlxs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sachi\Desktop\CAP776\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246332AF-1B0C-408E-AC20-BCDD6E89C5E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877F06B8-514A-412F-A28F-5646F2924F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="120">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -382,6 +382,24 @@
   </si>
   <si>
     <t xml:space="preserve">studied for my upcoming midterms </t>
+  </si>
+  <si>
+    <t>going back to college tomorrow and packing my stuff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reached college campus met  my friends and feeling good </t>
+  </si>
+  <si>
+    <t>tensed as it was first mid term exam today it went okay not that good</t>
+  </si>
+  <si>
+    <t>was my mid term today and was tired but iot went well</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prepared for my mid term exam </t>
+  </si>
+  <si>
+    <t>it was an holiday and I took rest and prepared for my exam</t>
   </si>
 </sst>
 </file>
@@ -3642,137 +3660,281 @@
         <v>113</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+    <row r="60" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A60" s="13">
+        <v>46305</v>
+      </c>
+      <c r="B60" s="14">
+        <v>500</v>
+      </c>
+      <c r="C60" s="14">
+        <v>30</v>
+      </c>
+      <c r="D60" s="14">
+        <v>60</v>
+      </c>
+      <c r="E60" s="14">
+        <v>30</v>
+      </c>
+      <c r="F60" s="14">
+        <v>0</v>
+      </c>
+      <c r="G60" s="14">
+        <v>0</v>
+      </c>
+      <c r="H60" s="14">
+        <v>500</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+        <v>320</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N60" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A61" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B61" s="14">
+        <v>450</v>
+      </c>
+      <c r="C61" s="14">
+        <v>0</v>
+      </c>
+      <c r="D61" s="14">
+        <v>120</v>
+      </c>
+      <c r="E61" s="14">
+        <v>30</v>
+      </c>
+      <c r="F61" s="14">
+        <v>0</v>
+      </c>
+      <c r="G61" s="14">
+        <v>0</v>
+      </c>
+      <c r="H61" s="14">
+        <v>500</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="17"/>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+        <v>340</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N61" s="17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A62" s="13">
+        <v>46307</v>
+      </c>
+      <c r="B62" s="14">
+        <v>200</v>
+      </c>
+      <c r="C62" s="14">
+        <v>0</v>
+      </c>
+      <c r="D62" s="14">
+        <v>180</v>
+      </c>
+      <c r="E62" s="14">
+        <v>0</v>
+      </c>
+      <c r="F62" s="14">
+        <v>0</v>
+      </c>
+      <c r="G62" s="14">
+        <v>0</v>
+      </c>
+      <c r="H62" s="14">
+        <v>400</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="17"/>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+        <v>660</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N62" s="17" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A63" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B63" s="14">
+        <v>180</v>
+      </c>
+      <c r="C63" s="14">
+        <v>0</v>
+      </c>
+      <c r="D63" s="14">
+        <v>120</v>
+      </c>
+      <c r="E63" s="14">
+        <v>0</v>
+      </c>
+      <c r="F63" s="14">
+        <v>0</v>
+      </c>
+      <c r="G63" s="14">
+        <v>0</v>
+      </c>
+      <c r="H63" s="14">
+        <v>400</v>
+      </c>
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>700</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="17"/>
+        <v>740</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N63" s="17" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+      <c r="A64" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B64" s="14">
+        <v>200</v>
+      </c>
+      <c r="C64" s="14">
+        <v>0</v>
+      </c>
+      <c r="D64" s="14">
+        <v>120</v>
+      </c>
+      <c r="E64" s="14">
+        <v>0</v>
+      </c>
+      <c r="F64" s="14">
+        <v>0</v>
+      </c>
+      <c r="G64" s="14">
+        <v>0</v>
+      </c>
+      <c r="H64" s="14">
+        <v>300</v>
+      </c>
+      <c r="I64" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>620</v>
+      </c>
+      <c r="J64" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="17"/>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N64" s="17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A65" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B65" s="14">
+        <v>180</v>
+      </c>
+      <c r="C65" s="14">
+        <v>30</v>
+      </c>
+      <c r="D65" s="14">
+        <v>240</v>
+      </c>
+      <c r="E65" s="14">
+        <v>0</v>
+      </c>
+      <c r="F65" s="14">
+        <v>0</v>
+      </c>
+      <c r="G65" s="14">
+        <v>0</v>
+      </c>
+      <c r="H65" s="14">
+        <v>250</v>
+      </c>
+      <c r="I65" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
+        <v>700</v>
+      </c>
+      <c r="J65" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="17"/>
+        <v>740</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N65" s="17" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" s="13"/>

--- a/12623846.xlxs.xlsx
+++ b/12623846.xlxs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sachi\Desktop\CAP776\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877F06B8-514A-412F-A28F-5646F2924F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{984923D6-B3EF-4F90-8A1E-1D290080C449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="121">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -400,6 +400,9 @@
   </si>
   <si>
     <t>it was an holiday and I took rest and prepared for my exam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feeling tired </t>
   </si>
 </sst>
 </file>
@@ -3937,26 +3940,50 @@
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
+      <c r="A66" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B66" s="14">
+        <v>300</v>
+      </c>
+      <c r="C66" s="14">
+        <v>30</v>
+      </c>
+      <c r="D66" s="14">
+        <v>120</v>
+      </c>
+      <c r="E66" s="14">
+        <v>0</v>
+      </c>
+      <c r="F66" s="14">
+        <v>0</v>
+      </c>
+      <c r="G66" s="14">
+        <v>0</v>
+      </c>
+      <c r="H66" s="14">
+        <v>400</v>
+      </c>
+      <c r="I66" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J66" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
-      <c r="N66" s="17"/>
+        <v>590</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="N66" s="17" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" s="13"/>
